--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4A02BA-6A95-44EC-8711-AC8BA0FE648C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A2F1DB-C6F7-4BC9-BA7B-DB6F806CD627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <si>
     <t>Nombre</t>
   </si>
@@ -586,6 +586,15 @@
   </si>
   <si>
     <t>Torales, Nicolás</t>
+  </si>
+  <si>
+    <t>Pérez, Tomás</t>
+  </si>
+  <si>
+    <t>Ferris, Nicolás</t>
+  </si>
+  <si>
+    <t>Martínez, Ignacio</t>
   </si>
 </sst>
 </file>
@@ -808,7 +817,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -827,9 +835,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1111,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E181"/>
+  <dimension ref="B2:E184"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" customWidth="1"/>
@@ -1398,7 +1407,7 @@
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="30" t="s">
         <v>180</v>
       </c>
       <c r="C30" s="24">
@@ -1495,7 +1504,7 @@
       <c r="E39" s="4"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="30" t="s">
         <v>179</v>
       </c>
       <c r="C40" s="24">
@@ -1808,7 +1817,7 @@
       <c r="E69" s="4"/>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B70" s="31" t="s">
+      <c r="B70" s="30" t="s">
         <v>178</v>
       </c>
       <c r="C70" s="24">
@@ -1830,7 +1839,7 @@
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B72" s="31" t="s">
+      <c r="B72" s="30" t="s">
         <v>173</v>
       </c>
       <c r="C72" s="27">
@@ -1841,16 +1850,19 @@
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B73" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
+      <c r="B73" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="C73" s="24">
+        <v>46280</v>
+      </c>
+      <c r="D73" s="24">
+        <v>46280</v>
+      </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -1858,7 +1870,7 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -1866,53 +1878,53 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C76" s="12">
-        <v>43890</v>
-      </c>
-      <c r="D76" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E76" s="13">
-        <v>27</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C77" s="8">
-        <v>45361</v>
-      </c>
-      <c r="D77" s="8">
-        <v>45403</v>
-      </c>
-      <c r="E77" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="C77" s="12">
+        <v>43890</v>
+      </c>
+      <c r="D77" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E77" s="13">
+        <v>27</v>
+      </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C78" s="8">
-        <v>45417</v>
+        <v>45361</v>
       </c>
       <c r="D78" s="8">
-        <v>45417</v>
+        <v>45403</v>
       </c>
       <c r="E78" s="4"/>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="C79" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D79" s="8">
+        <v>45417</v>
+      </c>
       <c r="E79" s="4"/>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -1920,64 +1932,64 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="4">
+      <c r="E81" s="4"/>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B82" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B82" s="19" t="s">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B83" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C82" s="20">
+      <c r="C83" s="20">
         <v>45913</v>
       </c>
-      <c r="D82" s="20">
+      <c r="D83" s="20">
         <v>45913</v>
       </c>
-      <c r="E82" s="4"/>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B83" s="1" t="s">
+      <c r="E83" s="4"/>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B84" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B84" s="31" t="s">
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B85" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="C84" s="24">
+      <c r="C85" s="24">
         <v>46252</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B85" s="31" t="s">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B86" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="C85" s="27">
+      <c r="C86" s="27">
         <v>46183</v>
       </c>
-      <c r="D85" s="27">
+      <c r="D86" s="27">
         <v>46183</v>
       </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B86" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -1985,43 +1997,43 @@
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C88" s="11">
-        <v>45255</v>
-      </c>
-      <c r="D88" s="11">
-        <v>45255</v>
-      </c>
-      <c r="E88" s="14">
-        <v>31</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C89" s="12">
-        <v>41832</v>
-      </c>
-      <c r="D89" s="12">
-        <v>41832</v>
-      </c>
-      <c r="E89" s="13">
-        <v>23</v>
+        <v>76</v>
+      </c>
+      <c r="C89" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D89" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E89" s="14">
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="C90" s="12">
+        <v>41832</v>
+      </c>
+      <c r="D90" s="12">
+        <v>41832</v>
+      </c>
+      <c r="E90" s="13">
+        <v>23</v>
+      </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -2029,7 +2041,7 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -2037,7 +2049,7 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
@@ -2045,83 +2057,89 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
-      <c r="E94" s="4">
-        <v>13</v>
-      </c>
+      <c r="E94" s="4"/>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
+      <c r="E95" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
-      <c r="E96" s="4">
-        <v>22</v>
-      </c>
+      <c r="E96" s="4"/>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
+      <c r="E97" s="4">
+        <v>22</v>
+      </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B98" s="19" t="s">
+      <c r="B98" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C98" s="5">
+        <v>45791</v>
+      </c>
+      <c r="D98" s="5">
+        <v>45806</v>
+      </c>
+      <c r="E98" s="4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B99" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="C98" s="21">
+      <c r="C99" s="21">
         <v>45892</v>
       </c>
-      <c r="D98" s="21">
+      <c r="D99" s="21">
         <v>45892</v>
       </c>
-      <c r="E98" s="4"/>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B99" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
       <c r="E99" s="4"/>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C100" s="16">
-        <v>44723</v>
-      </c>
-      <c r="D100" s="16">
-        <v>44723</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
       <c r="E100" s="4"/>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
+        <v>87</v>
+      </c>
+      <c r="C101" s="16">
+        <v>44723</v>
+      </c>
+      <c r="D101" s="16">
+        <v>44723</v>
+      </c>
       <c r="E101" s="4"/>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -2129,7 +2147,7 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
@@ -2137,7 +2155,7 @@
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
@@ -2145,7 +2163,7 @@
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
@@ -2153,7 +2171,7 @@
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
@@ -2161,7 +2179,7 @@
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
@@ -2169,7 +2187,7 @@
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
@@ -2177,37 +2195,38 @@
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C109" s="21">
-        <v>45689</v>
-      </c>
-      <c r="D109" s="21">
-        <v>45773</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
       <c r="E109" s="4"/>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="C110" s="21">
+        <v>45689</v>
+      </c>
+      <c r="D110" s="21">
+        <v>45773</v>
+      </c>
       <c r="E110" s="4"/>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B111" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4">
-        <v>4</v>
+      <c r="B111" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C111" s="24">
+        <v>46280</v>
+      </c>
+      <c r="D111" s="24">
+        <v>46280</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
@@ -2215,77 +2234,73 @@
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
+      <c r="E113" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C114" s="16">
-        <v>44961</v>
-      </c>
-      <c r="D114" s="16">
-        <v>45038</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
       <c r="E114" s="4"/>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C115" s="8">
-        <v>45403</v>
-      </c>
-      <c r="D115" s="8">
-        <v>45403</v>
-      </c>
-      <c r="E115" s="14">
-        <v>29</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C116" s="8">
-        <v>45346</v>
-      </c>
-      <c r="D116" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E116" s="14">
-        <v>10</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C116" s="16">
+        <v>44961</v>
+      </c>
+      <c r="D116" s="16">
+        <v>45038</v>
+      </c>
+      <c r="E116" s="4"/>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B117" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
-      <c r="E117" s="4"/>
+        <v>102</v>
+      </c>
+      <c r="C117" s="8">
+        <v>45403</v>
+      </c>
+      <c r="D117" s="8">
+        <v>45403</v>
+      </c>
+      <c r="E117" s="14">
+        <v>29</v>
+      </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B118" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C118" s="8">
-        <v>44961</v>
+        <v>45346</v>
       </c>
       <c r="D118" s="8">
-        <v>45080</v>
+        <v>45423</v>
       </c>
       <c r="E118" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
@@ -2293,121 +2308,127 @@
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B120" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-      <c r="E120" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="C120" s="8">
+        <v>44961</v>
+      </c>
+      <c r="D120" s="8">
+        <v>45080</v>
+      </c>
+      <c r="E120" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B122" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C122" s="24">
-        <v>46238</v>
-      </c>
+      <c r="B122" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B123" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B124" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C124" s="21">
-        <v>45885</v>
-      </c>
-      <c r="D124" s="21">
-        <v>45885</v>
-      </c>
-      <c r="E124" s="4"/>
+      <c r="B124" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C124" s="24">
+        <v>46238</v>
+      </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B125" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C125" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D125" s="8">
-        <v>45417</v>
-      </c>
-      <c r="E125" s="14">
-        <v>24</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4"/>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B126" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
+      <c r="B126" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C126" s="21">
+        <v>45885</v>
+      </c>
+      <c r="D126" s="21">
+        <v>45885</v>
+      </c>
       <c r="E126" s="4"/>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-      <c r="E127" s="4"/>
+        <v>110</v>
+      </c>
+      <c r="C127" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D127" s="8">
+        <v>45417</v>
+      </c>
+      <c r="E127" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C128" s="8">
-        <v>45556</v>
-      </c>
-      <c r="D128" s="8">
-        <v>45556</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
       <c r="E128" s="4"/>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B129" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C129" s="8">
-        <v>45273</v>
-      </c>
-      <c r="D129" s="8">
-        <v>45273</v>
-      </c>
+      <c r="B129" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
       <c r="E129" s="4"/>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
+        <v>113</v>
+      </c>
+      <c r="C130" s="8">
+        <v>45556</v>
+      </c>
+      <c r="D130" s="8">
+        <v>45556</v>
+      </c>
       <c r="E130" s="4"/>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B131" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
+      <c r="B131" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C131" s="8">
+        <v>45273</v>
+      </c>
+      <c r="D131" s="8">
+        <v>45273</v>
+      </c>
       <c r="E131" s="4"/>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -2415,7 +2436,7 @@
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
@@ -2423,7 +2444,7 @@
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B134" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
@@ -2431,21 +2452,15 @@
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C135" s="17">
-        <v>44247</v>
-      </c>
-      <c r="D135" s="17">
-        <v>44436</v>
-      </c>
-      <c r="E135" s="13">
-        <v>24</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
@@ -2453,15 +2468,21 @@
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
+        <v>120</v>
+      </c>
+      <c r="C137" s="17">
+        <v>44247</v>
+      </c>
+      <c r="D137" s="17">
+        <v>44436</v>
+      </c>
+      <c r="E137" s="13">
+        <v>24</v>
+      </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
@@ -2469,152 +2490,147 @@
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C139" s="12">
-        <v>44261</v>
-      </c>
-      <c r="D139" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E139" s="13">
-        <v>1</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B140" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="4"/>
+      <c r="B140" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C140" s="24">
+        <v>46270</v>
+      </c>
+      <c r="D140" s="24">
+        <v>46270</v>
+      </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B141" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="C141" s="24">
-        <v>45982</v>
-      </c>
+      <c r="B141" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B142" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C142" s="18">
-        <v>45220</v>
-      </c>
-      <c r="D142" s="18">
-        <v>45220</v>
-      </c>
-      <c r="E142" s="14">
-        <v>15</v>
+        <v>124</v>
+      </c>
+      <c r="C142" s="12">
+        <v>44261</v>
+      </c>
+      <c r="D142" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E142" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
-      <c r="E143" s="4">
-        <v>11</v>
-      </c>
+      <c r="E143" s="4"/>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B144" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C144" s="15">
-        <v>39760</v>
-      </c>
-      <c r="D144" s="4"/>
-      <c r="E144" s="4">
-        <v>3</v>
+      <c r="B144" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C144" s="24">
+        <v>45982</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
-      <c r="E145" s="4"/>
+        <v>126</v>
+      </c>
+      <c r="C145" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D145" s="18">
+        <v>45220</v>
+      </c>
+      <c r="E145" s="14">
+        <v>15</v>
+      </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C146" s="12">
-        <v>45003</v>
-      </c>
-      <c r="D146" s="12">
-        <v>45080</v>
-      </c>
-      <c r="E146" s="14">
-        <v>14</v>
+        <v>127</v>
+      </c>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4">
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C147" s="8">
-        <v>44811</v>
-      </c>
-      <c r="D147" s="8">
-        <v>44811</v>
-      </c>
-      <c r="E147" s="13">
-        <v>41</v>
+        <v>128</v>
+      </c>
+      <c r="C147" s="15">
+        <v>39760</v>
+      </c>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B148" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="C148" s="24">
-        <v>45993</v>
-      </c>
-      <c r="D148" s="24">
-        <v>45993</v>
-      </c>
+      <c r="B148" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C149" s="4"/>
-      <c r="D149" s="4"/>
-      <c r="E149" s="4"/>
+        <v>130</v>
+      </c>
+      <c r="C149" s="12">
+        <v>45003</v>
+      </c>
+      <c r="D149" s="12">
+        <v>45080</v>
+      </c>
+      <c r="E149" s="14">
+        <v>14</v>
+      </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C150" s="12">
-        <v>44739</v>
-      </c>
-      <c r="D150" s="12">
-        <v>44754</v>
+        <v>131</v>
+      </c>
+      <c r="C150" s="8">
+        <v>44811</v>
+      </c>
+      <c r="D150" s="8">
+        <v>44811</v>
       </c>
       <c r="E150" s="13">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B151" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C151" s="4"/>
-      <c r="D151" s="4"/>
-      <c r="E151" s="13">
-        <v>29</v>
+      <c r="B151" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C151" s="24">
+        <v>45993</v>
+      </c>
+      <c r="D151" s="24">
+        <v>45993</v>
       </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
@@ -2622,33 +2638,39 @@
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
-      <c r="E153" s="4"/>
+        <v>133</v>
+      </c>
+      <c r="C153" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D153" s="12">
+        <v>44754</v>
+      </c>
+      <c r="E153" s="13">
+        <v>37</v>
+      </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
+      <c r="E154" s="13">
+        <v>29</v>
+      </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
-      <c r="E155" s="4">
-        <v>18</v>
-      </c>
+      <c r="E155" s="4"/>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -2656,7 +2678,7 @@
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -2664,29 +2686,25 @@
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
-      <c r="E158" s="4"/>
+      <c r="E158" s="4">
+        <v>18</v>
+      </c>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C159" s="18">
-        <v>45097</v>
-      </c>
-      <c r="D159" s="18">
-        <v>45097</v>
-      </c>
-      <c r="E159" s="14">
-        <v>16</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
@@ -2694,7 +2712,7 @@
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
@@ -2702,15 +2720,21 @@
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C162" s="4"/>
-      <c r="D162" s="4"/>
-      <c r="E162" s="4"/>
+        <v>142</v>
+      </c>
+      <c r="C162" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D162" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E162" s="14">
+        <v>16</v>
+      </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
@@ -2718,27 +2742,23 @@
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B165" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C165" s="5">
-        <v>45585</v>
-      </c>
-      <c r="D165" s="5">
-        <v>45585</v>
-      </c>
+      <c r="B165" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
       <c r="E165" s="4"/>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
@@ -2746,29 +2766,27 @@
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C167" s="11">
-        <v>45423</v>
-      </c>
-      <c r="D167" s="11">
-        <v>45423</v>
-      </c>
-      <c r="E167" s="14">
-        <v>18</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="C167" s="4"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B168" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C168" s="4"/>
-      <c r="D168" s="4"/>
+      <c r="B168" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C168" s="5">
+        <v>45585</v>
+      </c>
+      <c r="D168" s="5">
+        <v>45585</v>
+      </c>
       <c r="E168" s="4"/>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
@@ -2776,131 +2794,171 @@
     </row>
     <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B170" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="C170" s="35"/>
-      <c r="D170" s="35"/>
-      <c r="E170" s="4"/>
+        <v>149</v>
+      </c>
+      <c r="C170" s="34">
+        <v>45423</v>
+      </c>
+      <c r="D170" s="34">
+        <v>45423</v>
+      </c>
+      <c r="E170" s="14">
+        <v>18</v>
+      </c>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C171" s="17">
-        <v>44660</v>
-      </c>
-      <c r="D171" s="17">
-        <v>44674</v>
-      </c>
-      <c r="E171" s="13">
-        <v>42</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B172" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="C172" s="22">
-        <v>44688</v>
-      </c>
-      <c r="D172" s="22">
-        <v>44688</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C172" s="4"/>
+      <c r="D172" s="4"/>
       <c r="E172" s="4"/>
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B173" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="C173" s="4"/>
-      <c r="D173" s="4"/>
-      <c r="E173" s="4">
-        <v>6</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C173" s="29"/>
+      <c r="D173" s="29"/>
+      <c r="E173" s="4"/>
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B174" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="C174" s="27">
-        <v>45494</v>
-      </c>
-      <c r="D174" s="27">
-        <v>45494</v>
-      </c>
-      <c r="E174" s="4"/>
+        <v>153</v>
+      </c>
+      <c r="C174" s="17">
+        <v>44660</v>
+      </c>
+      <c r="D174" s="17">
+        <v>44674</v>
+      </c>
+      <c r="E174" s="13">
+        <v>42</v>
+      </c>
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B175" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C175" s="30"/>
-      <c r="D175" s="30"/>
-      <c r="E175" s="4">
-        <v>20</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C175" s="22">
+        <v>44688</v>
+      </c>
+      <c r="D175" s="22">
+        <v>44688</v>
+      </c>
+      <c r="E175" s="4"/>
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B176" s="26" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
-      <c r="E176" s="4"/>
+      <c r="E176" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B177" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C177" s="32">
-        <v>42350</v>
-      </c>
-      <c r="D177" s="33">
-        <v>42532</v>
-      </c>
-      <c r="E177" s="13">
-        <v>21</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C177" s="27">
+        <v>45494</v>
+      </c>
+      <c r="D177" s="27">
+        <v>45494</v>
+      </c>
+      <c r="E177" s="4"/>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B178" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C178" s="29">
-        <v>44436</v>
-      </c>
-      <c r="D178" s="30"/>
-      <c r="E178" s="4"/>
+        <v>157</v>
+      </c>
+      <c r="C178" s="29"/>
+      <c r="D178" s="29"/>
+      <c r="E178" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B179" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C179" s="4"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="4"/>
+    </row>
+    <row r="180" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B180" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C180" s="31">
+        <v>42350</v>
+      </c>
+      <c r="D180" s="32">
+        <v>42532</v>
+      </c>
+      <c r="E180" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="181" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B181" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C181" s="28">
+        <v>44436</v>
+      </c>
+      <c r="D181" s="29"/>
+      <c r="E181" s="4"/>
+    </row>
+    <row r="182" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B182" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C179" s="28"/>
-      <c r="D179" s="28"/>
-    </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B180" s="23" t="s">
+      <c r="C182" s="35">
+        <v>45231</v>
+      </c>
+      <c r="D182" s="35">
+        <v>45231</v>
+      </c>
+      <c r="E182">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B183" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="C180" s="27">
+      <c r="C183" s="27">
         <v>45917</v>
       </c>
-      <c r="D180" s="27">
+      <c r="D183" s="27">
         <v>45917</v>
       </c>
-    </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B181" s="34" t="s">
+      <c r="E183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B184" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="C181" s="24">
+      <c r="C184" s="24">
         <v>46245</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E181">
-    <sortCondition ref="B2:B181"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E184">
+    <sortCondition ref="B2:B184"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A2F1DB-C6F7-4BC9-BA7B-DB6F806CD627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EB9BCC-7B70-4D99-BB0B-9D6B6CBCD82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t>Nombre</t>
   </si>
@@ -435,9 +435,6 @@
     <t>Rodríguez, Leandro</t>
   </si>
   <si>
-    <t>Rodríguez, Nicolás</t>
-  </si>
-  <si>
     <t>Rossi, Nicolás</t>
   </si>
   <si>
@@ -595,6 +592,15 @@
   </si>
   <si>
     <t>Martínez, Ignacio</t>
+  </si>
+  <si>
+    <t>Enrique, Nicolás</t>
+  </si>
+  <si>
+    <t>Gandini, Carlos</t>
+  </si>
+  <si>
+    <t>Chaves, Adrián</t>
   </si>
 </sst>
 </file>
@@ -736,7 +742,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -835,10 +841,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E184"/>
+  <dimension ref="B2:E186"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" customWidth="1"/>
@@ -1135,21 +1148,25 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" t="s">
         <v>162</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>163</v>
-      </c>
-      <c r="E2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+        <v>164</v>
+      </c>
+      <c r="C3" s="5">
+        <v>44716</v>
+      </c>
+      <c r="D3" s="5">
+        <v>44716</v>
+      </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -1164,8 +1181,12 @@
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="C5" s="5">
+        <v>45815</v>
+      </c>
+      <c r="D5" s="5">
+        <v>45815</v>
+      </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -1182,23 +1203,33 @@
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="C7" s="5">
+        <v>45756</v>
+      </c>
+      <c r="D7" s="5">
+        <v>45811</v>
+      </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="5">
+        <v>45822</v>
+      </c>
+      <c r="D8" s="5">
+        <v>45822</v>
+      </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="5">
+        <v>44394</v>
+      </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
@@ -1206,8 +1237,12 @@
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="5">
+        <v>44681</v>
+      </c>
+      <c r="D10" s="5">
+        <v>44681</v>
+      </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -1408,7 +1443,7 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C30" s="24">
         <v>46261</v>
@@ -1505,7 +1540,7 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C40" s="24">
         <v>46261</v>
@@ -1515,16 +1550,19 @@
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
+      <c r="B41" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C41" s="24">
+        <v>46291</v>
+      </c>
+      <c r="D41" s="35">
+        <v>46291</v>
+      </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -1532,7 +1570,7 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -1540,7 +1578,7 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -1548,7 +1586,7 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -1556,329 +1594,333 @@
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="8">
-        <v>45395</v>
-      </c>
-      <c r="D46" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E46" s="14">
-        <v>25</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="C47" s="8">
+        <v>45395</v>
+      </c>
+      <c r="D47" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E47" s="14">
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" s="12">
-        <v>43652</v>
-      </c>
-      <c r="D48" s="12">
-        <v>43722</v>
-      </c>
-      <c r="E48" s="13">
-        <v>12</v>
+        <v>42</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="C49" s="12">
+        <v>43652</v>
+      </c>
+      <c r="D49" s="12">
+        <v>43722</v>
+      </c>
+      <c r="E49" s="13">
+        <v>12</v>
+      </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C50" s="15">
-        <v>42294</v>
-      </c>
-      <c r="D50" s="12">
-        <v>42294</v>
-      </c>
-      <c r="E50" s="13">
-        <v>22</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="C51" s="15">
+        <v>42294</v>
+      </c>
+      <c r="D51" s="12">
+        <v>42294</v>
+      </c>
+      <c r="E51" s="13">
+        <v>22</v>
+      </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
-      <c r="E52" s="4">
-        <v>8</v>
-      </c>
+      <c r="E52" s="4"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C53" s="8">
-        <v>45395</v>
-      </c>
-      <c r="D53" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E53" s="14">
-        <v>9</v>
+        <v>47</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4">
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="12">
-        <v>42161</v>
-      </c>
-      <c r="E54" s="13">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="C54" s="8">
+        <v>45395</v>
+      </c>
+      <c r="D54" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E54" s="14">
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55" s="9">
-        <v>44739</v>
-      </c>
-      <c r="D55" s="9">
-        <v>44746</v>
-      </c>
-      <c r="E55" s="10">
-        <v>38</v>
+        <v>49</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="12">
+        <v>42161</v>
+      </c>
+      <c r="E55" s="13">
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C56" s="8">
-        <v>43708</v>
-      </c>
-      <c r="D56" s="8">
-        <v>44716</v>
-      </c>
-      <c r="E56" s="13">
-        <v>35</v>
+        <v>50</v>
+      </c>
+      <c r="C56" s="9">
+        <v>44739</v>
+      </c>
+      <c r="D56" s="9">
+        <v>44746</v>
+      </c>
+      <c r="E56" s="10">
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C57" s="8">
-        <v>44961</v>
+        <v>43708</v>
       </c>
       <c r="D57" s="8">
-        <v>45038</v>
+        <v>44716</v>
       </c>
       <c r="E57" s="13">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C58" s="8">
-        <v>45346</v>
+        <v>44961</v>
       </c>
       <c r="D58" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E58" s="14">
-        <v>24</v>
+        <v>45038</v>
+      </c>
+      <c r="E58" s="13">
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C59" s="8">
-        <v>45374</v>
+        <v>45346</v>
       </c>
       <c r="D59" s="8">
         <v>45423</v>
       </c>
-      <c r="E59" s="4"/>
+      <c r="E59" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="C60" s="8">
+        <v>45374</v>
+      </c>
+      <c r="D60" s="8">
+        <v>45423</v>
+      </c>
       <c r="E60" s="4"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C61" s="9">
-        <v>44226</v>
-      </c>
-      <c r="D61" s="9">
-        <v>44436</v>
-      </c>
-      <c r="E61" s="10">
-        <v>26</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="C62" s="9">
+        <v>44226</v>
+      </c>
+      <c r="D62" s="9">
+        <v>44436</v>
+      </c>
+      <c r="E62" s="10">
+        <v>26</v>
+      </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="12">
+      <c r="C64" s="4"/>
+      <c r="D64" s="12">
         <v>42161</v>
       </c>
-      <c r="E63" s="13">
+      <c r="E64" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B64" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C64" s="24">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B65" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C65" s="24">
         <v>46060</v>
       </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B67" s="19" t="s">
-        <v>181</v>
+      <c r="B67" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B68" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
+      <c r="B68" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C68" s="5">
+        <v>45738</v>
+      </c>
+      <c r="D68" s="5">
+        <v>46270</v>
+      </c>
       <c r="E68" s="4"/>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B69" s="1" t="s">
-        <v>62</v>
+      <c r="B69" s="19" t="s">
+        <v>180</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B70" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="C70" s="24">
-        <v>46256</v>
-      </c>
+      <c r="B70" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C71" s="11">
-        <v>45255</v>
-      </c>
-      <c r="D71" s="11">
-        <v>45255</v>
-      </c>
-      <c r="E71" s="14">
-        <v>8</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="C72" s="27">
+        <v>177</v>
+      </c>
+      <c r="C72" s="24">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B73" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C73" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D73" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E73" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B74" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C74" s="27">
         <v>46183</v>
       </c>
-      <c r="D72" s="27">
+      <c r="D74" s="27">
         <v>46183</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B73" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="C73" s="24">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B75" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C75" s="24">
         <v>46280</v>
       </c>
-      <c r="D73" s="24">
+      <c r="D75" s="24">
         <v>46280</v>
       </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B74" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B75" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -1886,154 +1928,145 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C77" s="12">
-        <v>43890</v>
-      </c>
-      <c r="D77" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E77" s="13">
-        <v>27</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C78" s="8">
-        <v>45361</v>
-      </c>
-      <c r="D78" s="8">
-        <v>45403</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
       <c r="E78" s="4"/>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C79" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D79" s="8">
-        <v>45417</v>
-      </c>
-      <c r="E79" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="C79" s="12">
+        <v>43890</v>
+      </c>
+      <c r="D79" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E79" s="13">
+        <v>27</v>
+      </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B80" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
+      <c r="B80" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C80" s="24">
+        <v>46291</v>
+      </c>
+      <c r="D80" s="24">
+        <v>46199</v>
+      </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="C81" s="8">
+        <v>45361</v>
+      </c>
+      <c r="D81" s="8">
+        <v>45403</v>
+      </c>
       <c r="E81" s="4"/>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4">
-        <v>14</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="C82" s="8">
+        <v>45417</v>
+      </c>
+      <c r="D82" s="8">
+        <v>45417</v>
+      </c>
+      <c r="E82" s="4"/>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B83" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C83" s="20">
-        <v>45913</v>
-      </c>
-      <c r="D83" s="20">
-        <v>45913</v>
-      </c>
+      <c r="B83" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
       <c r="E83" s="4"/>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B85" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="C85" s="24">
-        <v>46252</v>
+      <c r="B85" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4">
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B86" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="C86" s="27">
-        <v>46183</v>
-      </c>
-      <c r="D86" s="27">
-        <v>46183</v>
-      </c>
+      <c r="B86" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C86" s="20">
+        <v>45913</v>
+      </c>
+      <c r="D86" s="20">
+        <v>45913</v>
+      </c>
+      <c r="E86" s="4"/>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B88" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
+      <c r="B88" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="C88" s="24">
+        <v>46252</v>
+      </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B89" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C89" s="11">
-        <v>45255</v>
-      </c>
-      <c r="D89" s="11">
-        <v>45255</v>
-      </c>
-      <c r="E89" s="14">
-        <v>31</v>
+      <c r="B89" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C89" s="27">
+        <v>46183</v>
+      </c>
+      <c r="D89" s="27">
+        <v>46183</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C90" s="12">
-        <v>41832</v>
-      </c>
-      <c r="D90" s="12">
-        <v>41832</v>
-      </c>
-      <c r="E90" s="13">
-        <v>23</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -2041,23 +2074,35 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="C92" s="11">
+        <v>45255</v>
+      </c>
+      <c r="D92" s="11">
+        <v>45255</v>
+      </c>
+      <c r="E92" s="14">
+        <v>31</v>
+      </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="C93" s="12">
+        <v>41832</v>
+      </c>
+      <c r="D93" s="12">
+        <v>41832</v>
+      </c>
+      <c r="E93" s="13">
+        <v>23</v>
+      </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -2065,17 +2110,15 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
-      <c r="E95" s="4">
-        <v>13</v>
-      </c>
+      <c r="E95" s="4"/>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
@@ -2083,71 +2126,69 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
-      <c r="E97" s="4">
-        <v>22</v>
-      </c>
+      <c r="E97" s="4"/>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C98" s="5">
-        <v>45791</v>
-      </c>
-      <c r="D98" s="5">
-        <v>45806</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
       <c r="E98" s="4">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B99" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="C99" s="21">
-        <v>45892</v>
-      </c>
-      <c r="D99" s="21">
-        <v>45892</v>
-      </c>
+      <c r="B99" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
       <c r="E99" s="4"/>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
+      <c r="E100" s="4">
+        <v>22</v>
+      </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C101" s="16">
-        <v>44723</v>
-      </c>
-      <c r="D101" s="16">
-        <v>44723</v>
-      </c>
-      <c r="E101" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="C101" s="5">
+        <v>45791</v>
+      </c>
+      <c r="D101" s="5">
+        <v>45806</v>
+      </c>
+      <c r="E101" s="4">
+        <v>26</v>
+      </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B102" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
+      <c r="B102" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C102" s="21">
+        <v>45892</v>
+      </c>
+      <c r="D102" s="21">
+        <v>45892</v>
+      </c>
       <c r="E102" s="4"/>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
@@ -2155,15 +2196,19 @@
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
+        <v>87</v>
+      </c>
+      <c r="C104" s="16">
+        <v>44723</v>
+      </c>
+      <c r="D104" s="16">
+        <v>44723</v>
+      </c>
       <c r="E104" s="4"/>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
@@ -2171,7 +2216,7 @@
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
@@ -2179,7 +2224,7 @@
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
@@ -2187,7 +2232,7 @@
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
@@ -2195,7 +2240,7 @@
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -2203,30 +2248,23 @@
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C110" s="21">
-        <v>45689</v>
-      </c>
-      <c r="D110" s="21">
-        <v>45773</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
       <c r="E110" s="4"/>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B111" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="C111" s="24">
-        <v>46280</v>
-      </c>
-      <c r="D111" s="24">
-        <v>46280</v>
-      </c>
+      <c r="B111" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
@@ -2234,25 +2272,30 @@
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4">
-        <v>4</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C113" s="21">
+        <v>45689</v>
+      </c>
+      <c r="D113" s="21">
+        <v>45773</v>
+      </c>
+      <c r="E113" s="4"/>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B114" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
+      <c r="B114" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="C114" s="24">
+        <v>46280</v>
+      </c>
+      <c r="D114" s="24">
+        <v>46280</v>
+      </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
@@ -2260,77 +2303,73 @@
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C116" s="16">
-        <v>44961</v>
-      </c>
-      <c r="D116" s="16">
-        <v>45038</v>
-      </c>
-      <c r="E116" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B117" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C117" s="8">
-        <v>45403</v>
-      </c>
-      <c r="D117" s="8">
-        <v>45403</v>
-      </c>
-      <c r="E117" s="14">
-        <v>29</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B118" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C118" s="8">
-        <v>45346</v>
-      </c>
-      <c r="D118" s="8">
-        <v>45423</v>
-      </c>
-      <c r="E118" s="14">
-        <v>10</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B119" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="C119" s="16">
+        <v>44961</v>
+      </c>
+      <c r="D119" s="16">
+        <v>45038</v>
+      </c>
       <c r="E119" s="4"/>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B120" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C120" s="8">
-        <v>44961</v>
+        <v>45403</v>
       </c>
       <c r="D120" s="8">
-        <v>45080</v>
+        <v>45403</v>
       </c>
       <c r="E120" s="14">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B121" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
+        <v>103</v>
+      </c>
+      <c r="C121" s="8">
+        <v>45346</v>
+      </c>
+      <c r="D121" s="8">
+        <v>45423</v>
+      </c>
+      <c r="E121" s="14">
+        <v>10</v>
+      </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
@@ -2338,97 +2377,95 @@
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B123" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-      <c r="E123" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="C123" s="8">
+        <v>44961</v>
+      </c>
+      <c r="D123" s="8">
+        <v>45080</v>
+      </c>
+      <c r="E123" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B124" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="C124" s="24">
-        <v>46238</v>
-      </c>
+      <c r="B124" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B125" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B126" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C126" s="21">
-        <v>45885</v>
-      </c>
-      <c r="D126" s="21">
-        <v>45885</v>
-      </c>
+      <c r="B126" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
       <c r="E126" s="4"/>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B127" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C127" s="8">
-        <v>45417</v>
-      </c>
-      <c r="D127" s="8">
-        <v>45417</v>
-      </c>
-      <c r="E127" s="14">
-        <v>24</v>
+      <c r="B127" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="C127" s="24">
+        <v>46238</v>
       </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B129" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
+      <c r="B129" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C129" s="21">
+        <v>45885</v>
+      </c>
+      <c r="D129" s="21">
+        <v>45885</v>
+      </c>
       <c r="E129" s="4"/>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C130" s="8">
-        <v>45556</v>
+        <v>45417</v>
       </c>
       <c r="D130" s="8">
-        <v>45556</v>
-      </c>
-      <c r="E130" s="4"/>
+        <v>45417</v>
+      </c>
+      <c r="E130" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B131" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C131" s="8">
-        <v>45273</v>
-      </c>
-      <c r="D131" s="8">
-        <v>45273</v>
-      </c>
+      <c r="B131" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
       <c r="E131" s="4"/>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -2436,23 +2473,31 @@
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
+        <v>113</v>
+      </c>
+      <c r="C133" s="8">
+        <v>45556</v>
+      </c>
+      <c r="D133" s="8">
+        <v>45556</v>
+      </c>
       <c r="E133" s="4"/>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B134" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
+      <c r="B134" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C134" s="8">
+        <v>45273</v>
+      </c>
+      <c r="D134" s="8">
+        <v>45273</v>
+      </c>
       <c r="E134" s="4"/>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
@@ -2460,7 +2505,7 @@
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
@@ -2468,21 +2513,15 @@
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C137" s="17">
-        <v>44247</v>
-      </c>
-      <c r="D137" s="17">
-        <v>44436</v>
-      </c>
-      <c r="E137" s="13">
-        <v>24</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="4"/>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
@@ -2490,26 +2529,29 @@
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B140" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="C140" s="24">
-        <v>46270</v>
-      </c>
-      <c r="D140" s="24">
-        <v>46270</v>
+      <c r="B140" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C140" s="17">
+        <v>44247</v>
+      </c>
+      <c r="D140" s="17">
+        <v>44436</v>
+      </c>
+      <c r="E140" s="13">
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B141" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
@@ -2517,168 +2559,171 @@
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B142" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C142" s="12">
-        <v>44261</v>
-      </c>
-      <c r="D142" s="12">
-        <v>44436</v>
-      </c>
-      <c r="E142" s="13">
-        <v>1</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B143" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
-      <c r="E143" s="4"/>
+      <c r="B143" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="C143" s="24">
+        <v>46270</v>
+      </c>
+      <c r="D143" s="24">
+        <v>46270</v>
+      </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B144" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="C144" s="24">
-        <v>45982</v>
-      </c>
+      <c r="B144" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C145" s="18">
-        <v>45220</v>
-      </c>
-      <c r="D145" s="18">
-        <v>45220</v>
-      </c>
-      <c r="E145" s="14">
-        <v>15</v>
+        <v>124</v>
+      </c>
+      <c r="C145" s="12">
+        <v>44261</v>
+      </c>
+      <c r="D145" s="12">
+        <v>44436</v>
+      </c>
+      <c r="E145" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
-      <c r="E146" s="4">
-        <v>11</v>
-      </c>
+      <c r="E146" s="4"/>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B147" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C147" s="15">
-        <v>39760</v>
-      </c>
-      <c r="D147" s="4"/>
-      <c r="E147" s="4">
-        <v>3</v>
+      <c r="B147" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C147" s="24">
+        <v>45982</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C148" s="4"/>
-      <c r="D148" s="4"/>
-      <c r="E148" s="4"/>
+        <v>126</v>
+      </c>
+      <c r="C148" s="18">
+        <v>45220</v>
+      </c>
+      <c r="D148" s="18">
+        <v>45220</v>
+      </c>
+      <c r="E148" s="14">
+        <v>15</v>
+      </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C149" s="12">
-        <v>45003</v>
-      </c>
-      <c r="D149" s="12">
-        <v>45080</v>
-      </c>
-      <c r="E149" s="14">
-        <v>14</v>
+        <v>127</v>
+      </c>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4">
+        <v>11</v>
       </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C150" s="8">
-        <v>44811</v>
-      </c>
-      <c r="D150" s="8">
-        <v>44811</v>
-      </c>
-      <c r="E150" s="13">
-        <v>41</v>
+        <v>128</v>
+      </c>
+      <c r="C150" s="15">
+        <v>39760</v>
+      </c>
+      <c r="D150" s="4"/>
+      <c r="E150" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B151" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="C151" s="24">
-        <v>45993</v>
-      </c>
-      <c r="D151" s="24">
-        <v>45993</v>
-      </c>
+      <c r="B151" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C152" s="4"/>
-      <c r="D152" s="4"/>
-      <c r="E152" s="4"/>
+        <v>130</v>
+      </c>
+      <c r="C152" s="12">
+        <v>45003</v>
+      </c>
+      <c r="D152" s="12">
+        <v>45080</v>
+      </c>
+      <c r="E152" s="14">
+        <v>14</v>
+      </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C153" s="12">
-        <v>44739</v>
-      </c>
-      <c r="D153" s="12">
-        <v>44754</v>
+        <v>131</v>
+      </c>
+      <c r="C153" s="8">
+        <v>44811</v>
+      </c>
+      <c r="D153" s="8">
+        <v>44811</v>
       </c>
       <c r="E153" s="13">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B154" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C154" s="4"/>
-      <c r="D154" s="4"/>
-      <c r="E154" s="13">
-        <v>29</v>
+      <c r="B154" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C154" s="24">
+        <v>45993</v>
+      </c>
+      <c r="D154" s="24">
+        <v>45993</v>
       </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
+        <v>132</v>
+      </c>
+      <c r="C155" s="12">
+        <v>44739</v>
+      </c>
+      <c r="D155" s="12">
+        <v>44754</v>
+      </c>
+      <c r="E155" s="13">
+        <v>37</v>
+      </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
-      <c r="E156" s="4"/>
+      <c r="E156" s="13">
+        <v>29</v>
+      </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -2686,17 +2731,15 @@
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
-      <c r="E158" s="4">
-        <v>18</v>
-      </c>
+      <c r="E158" s="4"/>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
@@ -2704,15 +2747,17 @@
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
+      <c r="E160" s="4">
+        <v>18</v>
+      </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
@@ -2720,21 +2765,15 @@
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C162" s="18">
-        <v>45097</v>
-      </c>
-      <c r="D162" s="18">
-        <v>45097</v>
-      </c>
-      <c r="E162" s="14">
-        <v>16</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
@@ -2742,15 +2781,21 @@
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C164" s="4"/>
-      <c r="D164" s="4"/>
-      <c r="E164" s="4"/>
+        <v>141</v>
+      </c>
+      <c r="C164" s="18">
+        <v>45097</v>
+      </c>
+      <c r="D164" s="18">
+        <v>45097</v>
+      </c>
+      <c r="E164" s="14">
+        <v>16</v>
+      </c>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B165" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
@@ -2758,7 +2803,7 @@
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
@@ -2766,49 +2811,43 @@
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B168" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C168" s="5">
-        <v>45585</v>
-      </c>
-      <c r="D168" s="5">
-        <v>45585</v>
-      </c>
+      <c r="B168" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
       <c r="E168" s="4"/>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
     </row>
     <row r="170" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B170" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C170" s="34">
-        <v>45423</v>
-      </c>
-      <c r="D170" s="34">
-        <v>45423</v>
-      </c>
-      <c r="E170" s="14">
-        <v>18</v>
-      </c>
+      <c r="B170" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="C170" s="38">
+        <v>45585</v>
+      </c>
+      <c r="D170" s="38">
+        <v>45585</v>
+      </c>
+      <c r="E170" s="4"/>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171" s="26" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
@@ -2816,149 +2855,171 @@
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B172" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="C172" s="4"/>
-      <c r="D172" s="4"/>
-      <c r="E172" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="C172" s="37">
+        <v>45423</v>
+      </c>
+      <c r="D172" s="37">
+        <v>45423</v>
+      </c>
+      <c r="E172" s="14">
+        <v>18</v>
+      </c>
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B173" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="C173" s="29"/>
-      <c r="D173" s="29"/>
+        <v>149</v>
+      </c>
+      <c r="C173" s="4"/>
+      <c r="D173" s="4"/>
       <c r="E173" s="4"/>
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B174" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C174" s="17">
-        <v>44660</v>
-      </c>
-      <c r="D174" s="17">
-        <v>44674</v>
-      </c>
-      <c r="E174" s="13">
-        <v>42</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C174" s="4"/>
+      <c r="D174" s="4"/>
+      <c r="E174" s="4"/>
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B175" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="C175" s="22">
-        <v>44688</v>
-      </c>
-      <c r="D175" s="22">
-        <v>44688</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C175" s="29"/>
+      <c r="D175" s="29"/>
       <c r="E175" s="4"/>
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B176" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="C176" s="4"/>
-      <c r="D176" s="4"/>
-      <c r="E176" s="4">
-        <v>6</v>
+        <v>152</v>
+      </c>
+      <c r="C176" s="17">
+        <v>44660</v>
+      </c>
+      <c r="D176" s="17">
+        <v>44674</v>
+      </c>
+      <c r="E176" s="13">
+        <v>42</v>
       </c>
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B177" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="C177" s="27">
-        <v>45494</v>
-      </c>
-      <c r="D177" s="27">
-        <v>45494</v>
+        <v>153</v>
+      </c>
+      <c r="C177" s="22">
+        <v>44688</v>
+      </c>
+      <c r="D177" s="22">
+        <v>44688</v>
       </c>
       <c r="E177" s="4"/>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B178" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C178" s="29"/>
-      <c r="D178" s="29"/>
+        <v>154</v>
+      </c>
+      <c r="C178" s="4"/>
+      <c r="D178" s="4"/>
       <c r="E178" s="4">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B179" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="C179" s="4"/>
-      <c r="D179" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="C179" s="27">
+        <v>45494</v>
+      </c>
+      <c r="D179" s="27">
+        <v>45494</v>
+      </c>
       <c r="E179" s="4"/>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B180" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C180" s="31">
-        <v>42350</v>
-      </c>
-      <c r="D180" s="32">
-        <v>42532</v>
-      </c>
-      <c r="E180" s="13">
-        <v>21</v>
+        <v>156</v>
+      </c>
+      <c r="C180" s="29"/>
+      <c r="D180" s="29"/>
+      <c r="E180" s="4">
+        <v>20</v>
       </c>
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B181" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C181" s="28">
-        <v>44436</v>
-      </c>
-      <c r="D181" s="29"/>
+        <v>157</v>
+      </c>
+      <c r="C181" s="4"/>
+      <c r="D181" s="4"/>
       <c r="E181" s="4"/>
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B182" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="C182" s="35">
+        <v>158</v>
+      </c>
+      <c r="C182" s="31">
+        <v>42350</v>
+      </c>
+      <c r="D182" s="32">
+        <v>42532</v>
+      </c>
+      <c r="E182" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B183" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C183" s="28">
+        <v>44436</v>
+      </c>
+      <c r="D183" s="29"/>
+      <c r="E183" s="4"/>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B184" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C184" s="34">
         <v>45231</v>
       </c>
-      <c r="D182" s="35">
+      <c r="D184" s="34">
         <v>45231</v>
       </c>
-      <c r="E182">
+      <c r="E184">
         <v>93</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B183" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="C183" s="27">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B185" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="C185" s="27">
         <v>45917</v>
       </c>
-      <c r="D183" s="27">
+      <c r="D185" s="27">
         <v>45917</v>
       </c>
-      <c r="E183">
+      <c r="E185">
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B184" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="C184" s="24">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B186" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C186" s="24">
         <v>46245</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E184">
-    <sortCondition ref="B2:B184"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E186">
+    <sortCondition ref="B2:B186"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/backend/src/db/Jugadores_Historico.xlsx
+++ b/backend/src/db/Jugadores_Historico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eltri\Documents\GitHub\Brumario\backend\src\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EB9BCC-7B70-4D99-BB0B-9D6B6CBCD82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F50C18-9245-48A5-9600-5879DBA5FA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>Nombre</t>
   </si>
@@ -601,6 +601,9 @@
   </si>
   <si>
     <t>Chaves, Adrián</t>
+  </si>
+  <si>
+    <t>Willy, de Juampi</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E186"/>
+  <dimension ref="B2:E187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" customWidth="1"/>
@@ -2982,44 +2985,55 @@
       <c r="E183" s="4"/>
     </row>
     <row r="184" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B184" s="26" t="s">
+      <c r="B184" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="C184" s="24">
+        <v>46296</v>
+      </c>
+      <c r="D184" s="24">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B185" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="C184" s="34">
+      <c r="C185" s="34">
         <v>45231</v>
       </c>
-      <c r="D184" s="34">
+      <c r="D185" s="34">
         <v>45231</v>
       </c>
-      <c r="E184">
+      <c r="E185">
         <v>93</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B185" s="23" t="s">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B186" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="C185" s="27">
+      <c r="C186" s="27">
         <v>45917</v>
       </c>
-      <c r="D185" s="27">
+      <c r="D186" s="27">
         <v>45917</v>
       </c>
-      <c r="E185">
+      <c r="E186">
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B186" s="33" t="s">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B187" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="C186" s="24">
+      <c r="C187" s="24">
         <v>46245</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E186">
-    <sortCondition ref="B2:B186"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E187">
+    <sortCondition ref="B2:B187"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
